--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rb3fa918d0de04666"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R5fdf8b3aefaa4be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rceba3fc06e8d4467"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R9446ec381ddc4a27"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0901bbcbc8c9405f"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R7eee8c2fd0844d9a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rceba3fc06e8d4467"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R9446ec381ddc4a27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R3d58dbba2a054783"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Ra1d3c374d7374632"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R7eee8c2fd0844d9a"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf21d02c7635d48c9"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R3d58dbba2a054783"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Ra1d3c374d7374632"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rfa5f2e476cd34b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Red2a3b1135f84fa5"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf21d02c7635d48c9"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0d5be927893e43a9"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rfa5f2e476cd34b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Red2a3b1135f84fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rcd36efcb63204d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R55acf2b31aa648d5"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0d5be927893e43a9"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R34a532fb5cde47b1"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rcd36efcb63204d41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R55acf2b31aa648d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R8e7715d9fe8e4299"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rb29984d4b13942b7"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R34a532fb5cde47b1"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R279eeee034874806"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R8e7715d9fe8e4299"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rb29984d4b13942b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R4788e485931540f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R46700992fc9149db"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R279eeee034874806"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R20fa0aa908b44408"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R4788e485931540f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R46700992fc9149db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Ra68d2b3662b04db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R0e41e4a69a2643d0"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R20fa0aa908b44408"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc0605844d6fc40c2"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Ra68d2b3662b04db7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R0e41e4a69a2643d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rf6e2d6ce88c64de9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R6abdf105839b41ad"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc0605844d6fc40c2"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R995b67f85734489a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rf6e2d6ce88c64de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R6abdf105839b41ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rb3fb3d4b2cf749f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R29242dcb3fe846f5"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R995b67f85734489a"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R5b6a5876396c4430"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rb3fb3d4b2cf749f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R29242dcb3fe846f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R5753b84e850a4d75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R2c9e0abf98f5408a"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R5b6a5876396c4430"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rce04ef084adc46b3"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R5753b84e850a4d75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R2c9e0abf98f5408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R3688e353afd74de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rb5a2e4ddf7ed4611"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rce04ef084adc46b3"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R047d3f931b7f49d3"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R3688e353afd74de3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rb5a2e4ddf7ed4611"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rbfe63de3dfbb41f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R7ce6d0012f3c45b6"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R047d3f931b7f49d3"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1e9b5ff2434c4a91"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rbfe63de3dfbb41f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R7ce6d0012f3c45b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R27b89a0f8ee14408"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rf1950a9c2dd94f09"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1e9b5ff2434c4a91"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rff7506cc82bb4e8a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R27b89a0f8ee14408"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="Rf1950a9c2dd94f09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rbe1e891c3d25411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R5a402e7e0c104f0d"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rff7506cc82bb4e8a"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re6313939c0f14fad"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableAcrossSheets/output.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="Rbe1e891c3d25411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R5a402e7e0c104f0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" r:id="R91dfd3c61ad8491c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="2" r:id="R42ac790de8344190"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re6313939c0f14fad"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rebd8a6dcc97c4a07"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
